--- a/src/views/game/zlzq/cardList/laoduCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/laoduCard/z_level.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11790" windowHeight="10800" activeTab="2"/>
+    <workbookView windowWidth="11190" windowHeight="9990" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
     <sheet name="港口" sheetId="6" r:id="rId2"/>
     <sheet name="禅意" sheetId="7" r:id="rId3"/>
-    <sheet name="隐秘" sheetId="10" r:id="rId4"/>
+    <sheet name="老杜" sheetId="11" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="61">
   <si>
     <t>名称</t>
   </si>
@@ -47,19 +47,16 @@
     <t>圣殿卫士</t>
   </si>
   <si>
-    <t>修女</t>
-  </si>
-  <si>
-    <t>圣殿弩手</t>
-  </si>
-  <si>
     <t>增援战线</t>
   </si>
   <si>
     <t>田园守望者</t>
   </si>
   <si>
-    <t>光明惩戒</t>
+    <t>光明惩戒1</t>
+  </si>
+  <si>
+    <t>光明惩戒2</t>
   </si>
   <si>
     <t>小计：</t>
@@ -113,13 +110,22 @@
     <t>帝国卡等：</t>
   </si>
   <si>
-    <t>心灵黑洞</t>
+    <t>心灵黑洞1</t>
+  </si>
+  <si>
+    <t>心灵黑洞2</t>
+  </si>
+  <si>
+    <t>先发制人</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
   </si>
   <si>
     <t>黑夜突袭</t>
   </si>
   <si>
-    <t>狡诈学徒</t>
+    <t>黑金勒索者</t>
   </si>
   <si>
     <t>热血矿工</t>
@@ -134,6 +140,9 @@
     <t>海燕精卫</t>
   </si>
   <si>
+    <t>寒夜灯灵</t>
+  </si>
+  <si>
     <t>寻宝队长</t>
   </si>
   <si>
@@ -149,12 +158,12 @@
     <t>海燕·鲍莉</t>
   </si>
   <si>
-    <t>戴维的惊天计谋</t>
-  </si>
-  <si>
     <t>赤影·艾希尔</t>
   </si>
   <si>
+    <t>魔卡幻术师·梅基</t>
+  </si>
+  <si>
     <t>港口卡等：</t>
   </si>
   <si>
@@ -164,21 +173,24 @@
     <t>执剑道者</t>
   </si>
   <si>
+    <t>龟族僧人</t>
+  </si>
+  <si>
     <t>连击1</t>
   </si>
   <si>
     <t>连击2</t>
   </si>
   <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
-    <t>叶幻师</t>
-  </si>
-  <si>
     <t>铁山靠</t>
   </si>
   <si>
+    <t>风卷残云21</t>
+  </si>
+  <si>
+    <t>风卷残云2</t>
+  </si>
+  <si>
     <t>驱魔道人</t>
   </si>
   <si>
@@ -188,55 +200,19 @@
     <t>御风武者</t>
   </si>
   <si>
+    <t>泰山之力</t>
+  </si>
+  <si>
     <t>萌化术</t>
   </si>
   <si>
     <t>万物之灵</t>
   </si>
   <si>
-    <t>灵龟神丹</t>
-  </si>
-  <si>
     <t>悟能禅杖</t>
   </si>
   <si>
     <t>禅意卡等：</t>
-  </si>
-  <si>
-    <t>沉重否定</t>
-  </si>
-  <si>
-    <t>方尖魔碑</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>占卜命运</t>
-  </si>
-  <si>
-    <t>学仆-能源型</t>
-  </si>
-  <si>
-    <t>克隆术</t>
-  </si>
-  <si>
-    <t>白首魔根</t>
-  </si>
-  <si>
-    <t>心灵操控</t>
-  </si>
-  <si>
-    <t>魔像-钢翼仲裁者</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>No.3伊斯多维尔</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1208,7 +1184,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1219,7 +1195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1230,7 +1206,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1241,18 +1217,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1260,93 +1236,93 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1">
+        <f>AVERAGE(C2:C7)</f>
+        <v>21.5</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>21</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
       <c r="C15" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
@@ -1354,76 +1330,76 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C18" s="2">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="2">
+        <f>AVERAGE(C13:C18)</f>
+        <v>21.3333333333333</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="3">
         <v>4</v>
       </c>
-      <c r="C19" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="2">
-        <v>5</v>
-      </c>
-      <c r="C20" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="2">
-        <f>AVERAGE(C15:C20)</f>
-        <v>21</v>
+      <c r="C24" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
         <v>21</v>
@@ -1431,87 +1407,65 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="3">
+        <v>6</v>
+      </c>
+      <c r="C27" s="3">
         <v>20</v>
-      </c>
-      <c r="B27" s="3">
-        <v>4</v>
-      </c>
-      <c r="C27" s="3">
-        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C28" s="3">
         <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="3">
-        <v>6</v>
-      </c>
-      <c r="C29" s="3">
-        <v>20</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="3">
-        <v>8</v>
-      </c>
-      <c r="C30" s="3">
+      <c r="C31" s="3">
+        <f>AVERAGE(C24:C28)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="3" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="3">
-        <f>AVERAGE(C26:C30)</f>
-        <v>18.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="4" t="s">
+      <c r="B34" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="4">
-        <f>AVERAGE(C2:C9,C15:C20,C26:C30)</f>
-        <v>20.3157894736842</v>
+      <c r="C34" s="4">
+        <f>AVERAGE(C2:C7,C13:C18,C24:C28)</f>
+        <v>20.7058823529412</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C12" formulaRange="1"/>
+    <ignoredError sqref="C10" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1519,7 +1473,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1527,7 +1481,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1538,18 +1492,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -1557,21 +1511,21 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -1579,32 +1533,32 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
@@ -1615,60 +1569,60 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>20.1428571428571</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="2">
-        <v>4</v>
-      </c>
-      <c r="C15" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="C13" s="1">
+        <f>AVERAGE(C2:C10)</f>
+        <v>19.8888888888889</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1676,65 +1630,65 @@
         <v>36</v>
       </c>
       <c r="B17" s="2">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="2">
         <v>4</v>
       </c>
-      <c r="C17" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2">
+        <v>21</v>
+      </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="2">
+        <v>4</v>
+      </c>
+      <c r="C19" s="2">
+        <v>18</v>
+      </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="B20" s="2">
+        <v>4</v>
       </c>
       <c r="C20" s="2">
-        <f>AVERAGE(C14:C17)</f>
-        <v>18.5</v>
-      </c>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="3">
-        <v>2</v>
-      </c>
-      <c r="C23" s="3">
+      <c r="A23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="2">
+        <f>AVERAGE(C16:C20)</f>
         <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="3">
-        <v>3</v>
-      </c>
-      <c r="C24" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="3">
-        <v>3</v>
-      </c>
-      <c r="C25" s="3">
-        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1742,44 +1696,77 @@
         <v>40</v>
       </c>
       <c r="B26" s="3">
+        <v>2</v>
+      </c>
+      <c r="C26" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3">
+        <v>3</v>
+      </c>
+      <c r="C27" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3">
         <v>4</v>
       </c>
-      <c r="C26" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3">
+        <v>18</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="3">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="3">
+        <f>AVERAGE(C26:C29)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="3">
-        <f>AVERAGE(C23:C26)</f>
-        <v>16.25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C8,C14:C17,C23:C26)</f>
-        <v>18.6666666666667</v>
+      <c r="B35" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="4">
+        <f>AVERAGE(C2:C10,C16:C20,C26:C29)</f>
+        <v>19.2222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -1799,7 +1786,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1810,20 +1797,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1">
         <v>3</v>
@@ -1832,154 +1819,160 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>19.1428571428571</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="2">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="C12" s="1">
+        <f>AVERAGE(C2:C9)</f>
+        <v>18.5</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
       </c>
       <c r="C15" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2">
         <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="2">
-        <v>4</v>
-      </c>
-      <c r="C16" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
       </c>
       <c r="C18" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B19" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="2">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2"/>
@@ -1987,31 +1980,25 @@
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C14:C19)</f>
-        <v>16.3333333333333</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="3">
-        <v>3</v>
-      </c>
-      <c r="C25" s="3">
-        <v>12</v>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="2">
+        <f>AVERAGE(C15:C20)</f>
+        <v>16.8333333333333</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -2032,26 +2019,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C25:C26)</f>
+        <f>AVERAGE(C26:C26)</f>
         <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C8,C14:C19,C25:C26)</f>
-        <v>17.0666666666667</v>
+        <f>AVERAGE(C2:C9,C15:C20,C26:C26)</f>
+        <v>17.4</v>
       </c>
     </row>
   </sheetData>
@@ -2063,270 +2050,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="17.625" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="1">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="1">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>12.1428571428571</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="2">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="2">
-        <v>5</v>
-      </c>
-      <c r="C19" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C14:C19)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="3">
-        <v>5</v>
-      </c>
-      <c r="C25" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="3">
-        <v>9</v>
-      </c>
-      <c r="C26" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="3">
-        <f>AVERAGE(C25:C26)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C8,C14:C19,C25:C26)</f>
-        <v>12.0666666666667</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
